--- a/gs/departures.xlsx
+++ b/gs/departures.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RomeroJo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B843CE-7F5A-4DAA-8C9E-585ADB093D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944BB1D7-097B-44D3-BAC2-553C0E001C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DEPARTURE  SCHEDULE" sheetId="12" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="68">
   <si>
     <t>Union</t>
   </si>
@@ -82,9 +82,6 @@
     <t>CORU</t>
   </si>
   <si>
-    <t>Eddy Bonilla</t>
-  </si>
-  <si>
     <t>FAGU</t>
   </si>
   <si>
@@ -196,54 +193,9 @@
     <t>B62094</t>
   </si>
   <si>
-    <t>Jaime Rojas</t>
-  </si>
-  <si>
-    <t>JACQUES BIBRAC</t>
-  </si>
-  <si>
-    <t>Luis Polanco</t>
-  </si>
-  <si>
-    <t>Osvaldo Arrieta Falcon</t>
-  </si>
-  <si>
-    <t>José Ramiro Hernandez</t>
-  </si>
-  <si>
-    <t>Luis Alberto Guerra</t>
-  </si>
-  <si>
-    <t>Francisco Ramon de Dios</t>
-  </si>
-  <si>
-    <t>Roberto Carlos Dávila</t>
-  </si>
-  <si>
-    <t>Luis Trundle</t>
-  </si>
-  <si>
-    <t>Osmar Gonzalez</t>
-  </si>
-  <si>
-    <t>LUIS ALONSO AGUILLON LOPEZ</t>
-  </si>
-  <si>
-    <t>Aarón Omaña</t>
-  </si>
-  <si>
-    <t>Ammaran Williams</t>
-  </si>
-  <si>
-    <t>ALVIENNE LEAL</t>
-  </si>
-  <si>
     <t>Fort Lauderdale</t>
   </si>
   <si>
-    <t>Pastor Sessou's</t>
-  </si>
-  <si>
     <t>EAVU</t>
   </si>
   <si>
@@ -259,9 +211,6 @@
     <t>WEVU</t>
   </si>
   <si>
-    <t>Luis Jesse</t>
-  </si>
-  <si>
     <t>Global X</t>
   </si>
   <si>
@@ -293,6 +242,9 @@
   </si>
   <si>
     <t>5:00 PM - 6:50 PM</t>
+  </si>
+  <si>
+    <t>First Name Last Name</t>
   </si>
 </sst>
 </file>
@@ -1161,15 +1113,15 @@
     </row>
     <row r="8" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B9" s="15" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C9" s="16">
         <v>0.25</v>
@@ -1177,7 +1129,7 @@
     </row>
     <row r="10" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C10" s="16">
         <v>0.29166666666666669</v>
@@ -1185,7 +1137,7 @@
     </row>
     <row r="11" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B11" s="15" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="C11" s="16">
         <v>0.39583333333333331</v>
@@ -1193,7 +1145,7 @@
     </row>
     <row r="12" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B12" s="15" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C12" s="17">
         <v>0.4375</v>
@@ -1201,7 +1153,7 @@
     </row>
     <row r="13" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B13" s="15" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C13" s="16">
         <v>0.46875</v>
@@ -1209,15 +1161,15 @@
     </row>
     <row r="14" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B15" s="15" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C15" s="16">
         <v>0.60416666666666663</v>
@@ -1240,15 +1192,15 @@
     </row>
     <row r="21" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B21" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="14" t="s">
         <v>22</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C22" s="16">
         <v>0.25</v>
@@ -1256,7 +1208,7 @@
     </row>
     <row r="23" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C23" s="16">
         <v>0.29166666666666669</v>
@@ -1264,7 +1216,7 @@
     </row>
     <row r="24" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="C24" s="16">
         <v>0.39583333333333331</v>
@@ -1272,7 +1224,7 @@
     </row>
     <row r="25" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C25" s="17">
         <v>0.4375</v>
@@ -1280,7 +1232,7 @@
     </row>
     <row r="26" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C26" s="16">
         <v>0.4375</v>
@@ -1288,15 +1240,15 @@
     </row>
     <row r="27" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C28" s="16">
         <v>0.60416666666666663</v>
@@ -1349,7 +1301,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1357,22 +1309,22 @@
         <v>46239</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1380,13 +1332,13 @@
         <v>46239</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="22">
         <v>235</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="E3" s="22" t="s">
         <v>9</v>
@@ -1395,7 +1347,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1403,22 +1355,22 @@
         <v>46239</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="22">
         <v>1257</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1426,13 +1378,13 @@
         <v>46239</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E5" s="22" t="s">
         <v>3</v>
@@ -1441,7 +1393,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1452,19 +1404,19 @@
         <v>0.59375</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1472,22 +1424,22 @@
         <v>46239</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="22">
         <v>481</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1495,13 +1447,13 @@
         <v>46239</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E8" s="22" t="s">
         <v>8</v>
@@ -1510,7 +1462,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1518,22 +1470,22 @@
         <v>46239</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1541,13 +1493,13 @@
         <v>46239</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="E10" s="22" t="s">
         <v>12</v>
@@ -1556,13 +1508,13 @@
         <v>1</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="24"/>
@@ -1581,7 +1533,7 @@
     </row>
     <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D13" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="1"/>
@@ -1630,13 +1582,13 @@
         <v>2</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="24"/>
@@ -1655,16 +1607,16 @@
         <v>246</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="F3" s="1">
         <v>2</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1672,22 +1624,22 @@
         <v>46240</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" s="20">
         <v>200</v>
       </c>
       <c r="D4" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="22" t="s">
         <v>51</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>67</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1695,22 +1647,22 @@
         <v>46240</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1">
         <v>2</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1721,19 +1673,19 @@
         <v>0.55763888888888891</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>59</v>
+        <v>45</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>67</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1744,10 +1696,10 @@
         <v>0.56944444444444442</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E7" s="22" t="s">
         <v>10</v>
@@ -1756,7 +1708,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1767,10 +1719,10 @@
         <v>0.73888888888888893</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E8" s="22" t="s">
         <v>4</v>
@@ -1779,7 +1731,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1787,13 +1739,13 @@
         <v>46240</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" s="22">
         <v>2739</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E9" s="22" t="s">
         <v>11</v>
@@ -1802,13 +1754,13 @@
         <v>1</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="24"/>
@@ -1819,7 +1771,7 @@
     <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="24"/>
@@ -1830,11 +1782,11 @@
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="26" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E12" s="27"/>
       <c r="F12" s="1"/>
@@ -1848,19 +1800,19 @@
         <v>0.51736111111111105</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" s="1">
         <v>1</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1874,7 +1826,7 @@
     </row>
     <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D15" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="1"/>
